--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -3977,17 +3977,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7844,10 +7852,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
           <t>PCB_CCL_ABF材料</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
@@ -8010,10 +8022,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
           <t>PCB_CCL_ABF材料</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr">
         <is>
@@ -28529,11 +28545,27 @@
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -29317,11 +29349,27 @@
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -35045,15 +35093,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>矽智財_ASIC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -3327,7 +3327,11 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3501,7 +3505,11 @@
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3549,7 +3557,11 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3957,7 +3969,11 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4025,7 +4041,11 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4055,7 +4075,11 @@
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4157,7 +4181,11 @@
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4187,7 +4215,11 @@
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4253,7 +4285,11 @@
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4381,7 +4417,11 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4545,7 +4585,11 @@
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4575,7 +4619,11 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4767,7 +4815,11 @@
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4887,7 +4939,11 @@
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4971,7 +5027,11 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5037,7 +5097,11 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5067,7 +5131,11 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5373,15 +5441,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5483,7 +5559,11 @@
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5549,15 +5629,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5943,15 +6031,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6693,15 +6789,23 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>重電電網_電器電纜待細分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6841,15 +6945,23 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>重電電網_電器電纜待細分</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7003,7 +7115,11 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7051,7 +7167,11 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7081,7 +7201,11 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7147,7 +7271,11 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7177,7 +7305,11 @@
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7207,7 +7339,11 @@
       </c>
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7255,7 +7391,11 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7285,7 +7425,11 @@
       </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7603,7 +7747,11 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7765,7 +7913,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -7773,7 +7925,11 @@
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7931,7 +8087,11 @@
       </c>
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -7979,7 +8139,11 @@
       </c>
       <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8089,7 +8253,11 @@
           <t>造紙工業</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>造紙工業</t>
@@ -8097,7 +8265,11 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8115,7 +8287,11 @@
           <t>造紙工業</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>造紙工業</t>
@@ -8123,7 +8299,11 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8207,7 +8387,11 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8237,7 +8421,11 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8303,7 +8491,11 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8333,7 +8525,11 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8399,7 +8595,11 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr"/>
-      <c r="H392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8555,7 +8755,11 @@
       </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8639,7 +8843,11 @@
       </c>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8803,15 +9011,23 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>重電電網_電器電纜待細分</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9021,7 +9237,11 @@
       </c>
       <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9069,7 +9289,11 @@
       </c>
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9117,7 +9341,11 @@
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9183,7 +9411,11 @@
       </c>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9371,7 +9603,11 @@
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9743,15 +9979,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9769,15 +10013,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9813,15 +10065,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr"/>
-      <c r="H459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9873,15 +10133,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10041,15 +10309,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10067,15 +10343,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10123,15 +10407,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr"/>
-      <c r="H470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10149,15 +10441,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr"/>
-      <c r="H471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10175,15 +10475,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr"/>
-      <c r="H472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10201,15 +10509,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr"/>
-      <c r="H473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10227,15 +10543,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr"/>
-      <c r="H474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10253,15 +10577,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10279,15 +10611,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10305,15 +10645,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10331,15 +10679,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10433,15 +10789,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
-      <c r="H481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10477,15 +10841,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10521,15 +10893,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -10547,15 +10927,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -10675,15 +11063,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr"/>
-      <c r="H490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10735,15 +11131,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr"/>
-      <c r="H492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10761,15 +11165,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr"/>
-      <c r="H493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10787,15 +11199,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr"/>
-      <c r="H494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -10831,15 +11251,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10937,15 +11365,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10963,15 +11399,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr"/>
-      <c r="H500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11149,15 +11593,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11175,15 +11627,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11201,15 +11661,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11317,15 +11785,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11361,15 +11837,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11387,15 +11871,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11413,15 +11905,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11457,15 +11957,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11537,15 +12045,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11597,15 +12113,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11623,15 +12147,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11683,15 +12215,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11709,15 +12249,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11735,15 +12283,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11835,15 +12391,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12145,15 +12709,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12171,15 +12743,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12197,15 +12777,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12241,15 +12829,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12279,7 +12875,11 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12315,15 +12915,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12393,15 +13001,23 @@
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>資訊服務_AI軟體待細分</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12419,15 +13035,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12513,15 +13137,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12663,15 +13295,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -12807,15 +13447,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12833,15 +13481,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -13025,15 +13681,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13051,15 +13715,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13113,15 +13785,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13195,15 +13875,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13265,15 +13953,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13303,7 +13999,11 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13441,7 +14141,11 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13489,7 +14193,11 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13699,7 +14407,11 @@
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13729,7 +14441,11 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13831,7 +14547,11 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13879,7 +14599,11 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13909,7 +14633,11 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13939,7 +14667,11 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13987,7 +14719,11 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14071,7 +14807,11 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14173,7 +14913,11 @@
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14239,7 +14983,11 @@
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14357,7 +15105,11 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14459,7 +15211,11 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14489,7 +15245,11 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14789,7 +15549,11 @@
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15120,12 +15884,16 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15168,12 +15936,16 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15216,12 +15988,16 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15264,12 +16040,16 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -15294,12 +16074,16 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15342,12 +16126,16 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15372,12 +16160,16 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15438,12 +16230,16 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15468,12 +16264,16 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15498,12 +16298,16 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15528,12 +16332,16 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15558,12 +16366,16 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15588,12 +16400,16 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15618,12 +16434,16 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15648,12 +16468,16 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15678,12 +16502,16 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15726,12 +16554,16 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15756,12 +16588,16 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15786,12 +16622,16 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15816,12 +16656,16 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15846,12 +16690,16 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16301,15 +17149,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16345,15 +17201,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16439,15 +17303,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16465,15 +17337,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16491,15 +17371,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16517,15 +17405,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16573,15 +17469,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16703,15 +17607,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16763,15 +17675,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16789,15 +17709,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16863,15 +17791,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16907,15 +17843,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16933,15 +17877,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17007,15 +17959,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17033,15 +17993,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17059,15 +18027,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17155,15 +18131,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17215,15 +18199,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17279,15 +18271,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17305,15 +18305,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17331,15 +18339,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17423,15 +18439,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17485,15 +18509,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17547,15 +18579,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17573,15 +18613,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17617,15 +18665,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17661,15 +18717,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17927,15 +18991,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18165,15 +19237,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18227,15 +19307,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18409,15 +19497,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18609,15 +19705,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18687,15 +19791,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18815,15 +19927,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18859,15 +19979,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19009,15 +20137,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19263,15 +20399,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19325,15 +20469,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19493,15 +20645,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -19519,15 +20679,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -19581,15 +20749,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -19713,15 +20889,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
-      <c r="H386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -19811,15 +20995,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -19889,15 +21081,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -19981,15 +21181,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -20007,15 +21215,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -20033,15 +21249,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -20059,15 +21283,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -20103,15 +21335,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -20181,15 +21421,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -20369,15 +21617,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -20619,15 +21875,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20933,15 +22197,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20977,15 +22249,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -21111,15 +22391,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -21209,15 +22497,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -21235,15 +22531,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -21345,15 +22649,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -21407,15 +22719,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21433,7 +22753,11 @@
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>綠能環保</t>
@@ -21441,7 +22765,11 @@
       </c>
       <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21621,15 +22949,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -21665,15 +23001,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -21775,15 +23119,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -21801,15 +23153,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -21919,15 +23279,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr"/>
-      <c r="H489" t="inlineStr"/>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22279,15 +23647,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22359,15 +23735,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22385,15 +23769,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22517,15 +23909,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22579,15 +23979,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22677,15 +24085,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22739,15 +24155,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22765,15 +24189,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22791,15 +24223,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23005,15 +24445,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -23031,15 +24479,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23075,15 +24531,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23101,15 +24565,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23621,7 +25093,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -23629,7 +25105,11 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23845,7 +25325,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -23853,7 +25337,11 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24225,7 +25713,11 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -24621,15 +26113,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -24683,15 +26183,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24781,15 +26289,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -24897,15 +26413,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25085,15 +26609,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -25201,15 +26733,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -25263,15 +26803,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -25325,15 +26873,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -25809,15 +27365,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -25901,7 +27465,11 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -25937,7 +27505,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -25945,7 +27517,11 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -26035,15 +27611,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -26145,7 +27729,11 @@
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -26319,7 +27907,11 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -26337,15 +27929,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -26521,15 +28121,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -26547,15 +28155,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -26665,15 +28281,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -26761,15 +28385,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -26911,15 +28543,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -26973,15 +28613,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -27017,15 +28665,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -27095,15 +28751,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -27151,15 +28815,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -27267,15 +28939,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -27359,15 +29039,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -27487,7 +29175,11 @@
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -27769,7 +29461,11 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -27967,15 +29663,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -28083,15 +29787,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -28397,15 +30109,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -28761,15 +30481,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -28857,15 +30585,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -29077,15 +30813,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr"/>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -29121,15 +30865,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -29271,15 +31023,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -29297,15 +31057,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -29423,15 +31191,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -29449,15 +31225,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -29565,15 +31349,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -29675,7 +31467,11 @@
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -29777,7 +31573,11 @@
       </c>
       <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -30260,12 +32060,16 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -30308,12 +32112,16 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -30446,12 +32254,16 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -30476,12 +32288,16 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -30596,12 +32412,16 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -30673,15 +32493,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -30699,15 +32527,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -30833,15 +32669,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -30895,15 +32739,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -31005,15 +32857,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -31031,15 +32891,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
-      <c r="H436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -31057,15 +32925,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -31137,15 +33013,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -31217,15 +33101,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -31261,15 +33153,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -31431,15 +33331,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -31457,15 +33365,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -31501,15 +33417,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr"/>
-      <c r="H459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -31599,15 +33523,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -31713,15 +33645,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr"/>
-      <c r="H469" t="inlineStr"/>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -31867,15 +33807,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -31905,7 +33853,11 @@
       </c>
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -32105,15 +34057,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -32351,15 +34311,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr"/>
-      <c r="H498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -32567,15 +34535,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32663,15 +34639,23 @@
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>資訊服務_AI軟體待細分</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32689,15 +34673,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32751,15 +34743,23 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>網通_低軌衛星待細分</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32883,15 +34883,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32927,15 +34935,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -33091,15 +35107,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -33331,15 +35355,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -33429,15 +35461,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -33473,15 +35513,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -33649,15 +35697,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -33711,15 +35767,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -33755,15 +35819,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33949,15 +36021,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -34009,15 +36089,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -34143,15 +36231,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -34241,15 +36337,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -34303,15 +36407,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -34329,7 +36441,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -34337,7 +36453,11 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -34385,15 +36505,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -34411,15 +36539,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -34455,15 +36591,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -34625,15 +36769,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -34777,7 +36929,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -34785,7 +36941,11 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -34821,7 +36981,11 @@
           <t>油電燃氣業</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>油電燃氣業</t>
@@ -34829,7 +36993,11 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -35271,7 +37439,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -35279,7 +37451,11 @@
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -35297,15 +37473,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -35377,15 +37561,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -35493,15 +37685,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -35735,15 +37935,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -36517,15 +38725,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -36759,15 +38975,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -36905,15 +39129,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -37249,7 +39481,11 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -37315,7 +39551,11 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -37423,15 +39663,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -37485,15 +39733,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -37873,15 +40129,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -37935,15 +40199,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -38069,15 +40341,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -38149,7 +40429,11 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>生技醫療業</t>
@@ -38157,7 +40441,11 @@
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -38303,7 +40591,11 @@
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>綠能環保</t>
@@ -38311,7 +40603,11 @@
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -39177,15 +41473,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -39347,7 +41651,11 @@
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>綠能環保</t>
@@ -39355,7 +41663,11 @@
       </c>
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -43975,15 +46287,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -44289,7 +46609,11 @@
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>綠能環保</t>
@@ -44297,7 +46621,11 @@
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -44531,15 +46859,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -44631,7 +46967,11 @@
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -44685,15 +47025,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -45071,15 +47419,23 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>AI供應鏈_其他電子待細分</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -45517,15 +47873,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -45651,15 +48015,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -45677,15 +48049,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -45721,15 +48101,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -45801,15 +48189,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -45933,15 +48329,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -46031,15 +48435,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -46129,15 +48541,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -46155,15 +48575,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -46181,15 +48609,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -46225,15 +48661,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -46251,15 +48695,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -46295,15 +48747,23 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子通路_IC通路待細分</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -46357,15 +48817,23 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>半導體業_待細分</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -46383,15 +48851,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -46479,15 +48955,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -46595,15 +49079,23 @@
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>AI_PC_電腦週邊待細分</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -46621,15 +49113,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -46647,15 +49147,23 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>光電_CPO光通訊待細分</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -46757,15 +49265,23 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件_待細分</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -47127,15 +49643,23 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>機器人自動化_電機機械待細分</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -47675,15 +50199,23 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>數位雲端_AI服務待細分</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -47827,7 +50359,11 @@
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>綠能環保</t>
@@ -47835,7 +50371,11 @@
       </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -48489,7 +51029,11 @@
           <t>存託憑證</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>存託憑證</t>
@@ -48497,7 +51041,11 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -48677,7 +51225,11 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>運動休閒</t>
@@ -48685,7 +51237,11 @@
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -48739,7 +51295,11 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>運動休閒</t>
@@ -48747,7 +51307,11 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -49323,7 +51887,11 @@
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -7295,19 +7295,27 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>化學工業</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
+          <t>特化材料</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>特化化學</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>電子材料</t>
+        </is>
+      </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_specialty_theme_20260530</t>
         </is>
       </c>
     </row>
@@ -7497,11 +7505,31 @@
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>特化材料</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>特化化學</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>電子材料</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>user_authorized_specialty_theme_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +425,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -506,57 +494,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>??/???</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>????1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>??2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>??3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>report_line_memberships</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>non_mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -5723,11 +5711,7 @@
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
@@ -8490,11 +8474,7 @@
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
@@ -10895,15 +10875,31 @@
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
-      <c r="B373" t="inlineStr"/>
-      <c r="C373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>non_mainstream</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -10913,10 +10909,14 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -15366,57 +15366,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>??/???</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>????1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>??2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>??3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>report_line_memberships</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>non_mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -16347,36 +16347,20 @@
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -16384,11 +16368,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -16663,11 +16643,7 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>??</t>
@@ -17768,11 +17744,7 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>??</t>
@@ -18435,20 +18407,36 @@
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>光電_CPO光通訊待細分</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -18456,7 +18444,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -19369,15 +19361,31 @@
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>non_mainstream</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -19387,10 +19395,14 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -23996,36 +24008,20 @@
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -24033,11 +24029,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -30998,7 +30990,11 @@
       </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="G480" t="inlineStr">
         <is>
           <t>??</t>
@@ -31678,57 +31674,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>??/???</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>????1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>??2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>??3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>report_line_memberships</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>non_mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -32141,36 +32137,20 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -32178,11 +32158,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -37594,31 +37570,15 @@
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>non_mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -37628,14 +37588,10 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -39984,36 +39940,20 @@
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -40021,11 +39961,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
@@ -44073,36 +44009,20 @@
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -44110,11 +44030,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -46196,20 +46112,36 @@
     </row>
     <row r="494">
       <c r="A494" t="inlineStr"/>
-      <c r="B494" t="inlineStr"/>
-      <c r="C494" t="inlineStr"/>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>電子零組件_待細分</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -46217,7 +46149,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr"/>
@@ -46442,57 +46378,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>??/???</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>????1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>??2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>??3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>report_line_memberships</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>non_mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -50884,36 +50820,20 @@
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>半導體_設備材料待細分</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -50921,11 +50841,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -54289,20 +54205,36 @@
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AI_PC_電腦週邊待細分</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -54310,7 +54242,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
@@ -60254,57 +60190,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>??/???</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>????1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>??2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>??3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>report_line_memberships</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>non_mainstream_report_eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>??</t>
         </is>
@@ -65919,36 +65855,20 @@
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>光電_CPO光通訊待細分</t>
-        </is>
-      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -65956,11 +65876,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -66301,11 +66217,7 @@
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>??</t>
@@ -68088,36 +68000,20 @@
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>數位雲端_AI應用待細分</t>
-        </is>
-      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -68125,11 +68021,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
@@ -68778,15 +68670,31 @@
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>non_mainstream</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -68796,10 +68704,14 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
@@ -69497,31 +69409,15 @@
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
-          <t>non_mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -69531,14 +69427,10 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -9296,20 +9296,36 @@
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
-      <c r="B322" t="inlineStr"/>
-      <c r="C322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>重電電網_電器電纜待細分</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -9317,7 +9333,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>industry_fallback_from_listed_company_classification_needed;provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -9848,31 +9868,15 @@
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>化學工業</t>
-        </is>
-      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
-          <t>non_mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -9882,14 +9886,10 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr"/>
@@ -14582,20 +14582,36 @@
     </row>
     <row r="484">
       <c r="A484" t="inlineStr"/>
-      <c r="B484" t="inlineStr"/>
-      <c r="C484" t="inlineStr"/>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>半導體_設備材料待細分</t>
+        </is>
+      </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -14603,7 +14619,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr"/>
@@ -16747,20 +16767,36 @@
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>光電_CPO光通訊待細分</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -16768,7 +16804,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -31902,36 +31942,20 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>半導體_設備材料待細分</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -31939,11 +31963,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -32835,36 +32855,20 @@
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>半導體_設備材料待細分</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>mainstream</t>
+          <t>theme_unknown</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -32872,11 +32876,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -45261,7 +45261,11 @@
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="G467" t="inlineStr">
         <is>
           <t>??</t>
@@ -65855,20 +65859,36 @@
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>光電_CPO光通訊待細分</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>theme_unknown</t>
+          <t>mainstream</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -65876,7 +65896,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -460,46 +460,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>族群1</t>
+          <t>基本族群</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>填最重要族群，例如機器人自動化、玻纖布、低軌衛星、被動元件。</t>
+          <t>每檔股票都應有一個常態分類，例如電機機械、通信網路、塑膠、金融保險。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>族群2/族群3/族群4/族群5</t>
+          <t>熱門族群1～熱門族群5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>同一股票有多個族群時再填。</t>
+          <t>只填資金題材或你要納入熱門族群模型的標籤，例如機器人自動化、玻纖布、低軌衛星、被動元件。留空時不進入熱門族群回檔模型。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>產業預設/題材預設/最終分流/雙重身分</t>
+          <t>備註</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>程式參考欄，通常不用改。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
         <is>
           <t>需要說明來源或例外時填。</t>
         </is>
@@ -516,26 +504,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,70 +538,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>基本族群</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>族群1</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>族群2</t>
+          <t>熱門族群1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>族群3</t>
+          <t>熱門族群2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>族群4</t>
+          <t>熱門族群3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>族群5</t>
+          <t>熱門族群4</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>產業預設</t>
+          <t>熱門族群5</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>題材預設</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>最終分流</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>雙重身分</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>report_line_memberships</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mainstream_report_eligible</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>non_mainstream_report_eligible</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -643,50 +595,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>主流</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>機器人自動化</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>mainstream</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,12 +426,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -525,57 +513,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -18641,57 +18629,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -22395,12 +22383,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -23649,12 +23637,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -37389,57 +37377,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -55965,57 +55953,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -61900,12 +61888,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -73825,57 +73813,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -79467,12 +79455,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -86561,12 +86549,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -86660,12 +86648,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -11300,12 +11300,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16343,17 +16343,17 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -16361,11 +16361,7 @@
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -22383,12 +22379,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -23637,12 +23633,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -29413,17 +29409,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -29431,11 +29427,7 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -32730,12 +32722,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -32748,7 +32740,11 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -45167,17 +45163,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -45594,17 +45590,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -45612,11 +45608,7 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -48410,12 +48402,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -49512,12 +49504,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -57074,17 +57066,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -57092,7 +57084,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -77411,17 +77407,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -85799,12 +85795,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,12 +438,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -513,57 +525,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -18625,57 +18637,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -37373,57 +37385,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -55945,57 +55957,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -73809,57 +73821,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,12 +426,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -525,57 +513,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -18633,57 +18621,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -37381,57 +37369,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -55953,57 +55941,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -73821,57 +73809,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -86611,12 +86611,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -46210,7 +46210,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>緯致</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -52522,12 +52522,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -52744,12 +52744,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -53480,12 +53480,12 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -54549,12 +54549,12 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -55079,12 +55079,12 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -61736,12 +61736,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -78398,12 +78398,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -84951,17 +84951,17 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -84969,7 +84969,11 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -85828,12 +85832,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -86034,12 +86038,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86104,12 +86108,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86578,12 +86582,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86677,12 +86681,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -86813,12 +86817,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -52131,12 +52131,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -61736,12 +61736,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -67124,12 +67124,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -85371,12 +85371,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -85389,7 +85389,11 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -85832,12 +85836,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -86038,12 +86042,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86108,12 +86112,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86446,12 +86450,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86582,12 +86586,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86681,12 +86685,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -86817,12 +86821,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -52131,12 +52131,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -61736,12 +61736,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -67124,12 +67124,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -85371,12 +85371,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -85389,11 +85389,7 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -85836,12 +85832,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -86042,12 +86038,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86112,12 +86108,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86450,12 +86446,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86586,12 +86582,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86685,12 +86681,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -86821,12 +86817,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,12 +438,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -513,57 +525,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -18621,57 +18633,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -37369,57 +37381,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -55941,57 +55953,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -73809,57 +73821,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -23666,12 +23666,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -48435,12 +48435,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -52131,12 +52131,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -61736,12 +61736,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -67124,12 +67124,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -86623,12 +86623,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -86656,12 +86656,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86722,12 +86722,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -17871,12 +17871,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -23666,12 +23666,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -33916,19 +33916,15 @@
           <t>台興</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
+      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>普通股_待補官方產業</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -33936,11 +33932,7 @@
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -85873,12 +85865,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -86487,12 +86479,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86689,12 +86681,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -17871,12 +17871,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -23666,12 +23666,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -85865,12 +85865,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -86479,12 +86479,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86681,12 +86681,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -48427,12 +48427,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -86071,12 +86071,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86615,12 +86615,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -86648,12 +86648,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86681,12 +86681,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,12 +438,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -513,57 +525,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -582,12 +594,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -615,12 +627,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -648,12 +660,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -681,12 +693,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -714,12 +726,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -747,12 +759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -780,12 +792,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -813,12 +825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,12 +858,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -879,12 +891,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -912,12 +924,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -945,12 +957,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -978,12 +990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1011,12 +1023,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1044,12 +1056,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1077,12 +1089,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1110,12 +1122,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1143,12 +1155,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1176,12 +1188,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1209,12 +1221,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1242,12 +1254,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1275,12 +1287,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1308,12 +1320,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1341,12 +1353,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1374,12 +1386,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1407,12 +1419,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1440,12 +1452,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1473,12 +1485,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1506,12 +1518,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1539,12 +1551,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1572,12 +1584,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1605,12 +1617,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1638,12 +1650,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1671,12 +1683,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1704,12 +1716,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1737,12 +1749,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1770,12 +1782,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1803,12 +1815,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1836,12 +1848,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1869,12 +1881,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1902,12 +1914,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1935,12 +1947,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1968,12 +1980,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2001,12 +2013,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2034,12 +2046,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2067,12 +2079,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2100,12 +2112,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2133,12 +2145,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2166,12 +2178,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2199,12 +2211,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2232,12 +2244,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2265,12 +2277,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2298,12 +2310,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2331,12 +2343,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2364,12 +2376,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2397,12 +2409,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2430,12 +2442,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2463,12 +2475,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2496,12 +2508,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2529,12 +2541,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2562,12 +2574,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2595,12 +2607,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2628,12 +2640,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2661,12 +2673,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2694,12 +2706,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2727,12 +2739,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2760,12 +2772,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2793,12 +2805,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2826,12 +2838,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2859,12 +2871,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2892,12 +2904,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2925,12 +2937,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2958,12 +2970,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2991,12 +3003,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3024,12 +3036,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3057,12 +3069,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3090,12 +3102,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3123,12 +3135,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3156,12 +3168,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3189,12 +3201,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3222,12 +3234,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3255,12 +3267,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3288,12 +3300,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3321,12 +3333,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3354,12 +3366,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3387,12 +3399,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3420,12 +3432,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3453,12 +3465,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3486,12 +3498,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3519,12 +3531,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3552,12 +3564,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3585,12 +3597,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3618,12 +3630,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3651,12 +3663,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3684,12 +3696,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3717,12 +3729,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3750,12 +3762,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3783,12 +3795,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3816,12 +3828,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3849,12 +3861,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3882,12 +3894,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3915,12 +3927,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3948,12 +3960,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3981,12 +3993,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4014,12 +4026,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4047,12 +4059,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4080,12 +4092,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4113,12 +4125,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4146,12 +4158,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4179,12 +4191,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4212,12 +4224,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4245,12 +4257,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4278,12 +4290,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4311,12 +4323,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4344,12 +4356,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4377,12 +4389,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4410,12 +4422,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4443,12 +4455,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4476,12 +4488,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4509,12 +4521,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4542,12 +4554,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4575,12 +4587,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4608,12 +4620,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4641,12 +4653,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4674,12 +4686,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4707,12 +4719,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4740,12 +4752,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4773,12 +4785,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4806,12 +4818,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4839,12 +4851,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4872,12 +4884,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4905,12 +4917,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4938,12 +4950,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4971,12 +4983,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5004,12 +5016,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5037,12 +5049,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5070,12 +5082,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5103,12 +5115,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5136,12 +5148,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5169,12 +5181,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5202,12 +5214,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5235,12 +5247,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5268,12 +5280,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5301,12 +5313,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5334,12 +5346,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5367,12 +5379,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5400,12 +5412,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5433,12 +5445,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5466,12 +5478,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5499,12 +5511,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5532,12 +5544,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5565,12 +5577,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5598,12 +5610,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>指數/ETF/ETN商品</t>
+          <t>指數 / ETF / ETN商品</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7781,12 +7793,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>TPU材料 / 工業複合材料</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>TPU材料 / 工業複合材料</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -17871,12 +17883,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>房地產代銷 / 建設服務</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>房地產代銷 / 建設服務</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -18621,57 +18633,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -37361,57 +37373,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -52123,12 +52135,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>租賃金融 / 企業融資</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>租賃金融 / 企業融資</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -55933,57 +55945,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -61728,12 +61740,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>TPU材料 / 工業複合材料</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>TPU材料 / 工業複合材料</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -67116,12 +67128,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>投資控股 / 創投</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>投資控股 / 創投</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -73805,57 +73817,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -78427,12 +78439,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -85326,12 +85338,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -85363,12 +85375,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -85400,12 +85412,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -85437,12 +85449,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -85474,12 +85486,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -85511,12 +85523,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -85548,12 +85560,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -85585,12 +85597,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -85622,12 +85634,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85659,12 +85671,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85865,12 +85877,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -86071,12 +86083,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86479,12 +86491,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86714,12 +86726,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -86850,12 +86862,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,12 +426,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>填寫方式</t>
         </is>
@@ -525,57 +513,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -18633,57 +18621,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -37373,57 +37361,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -55945,57 +55933,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -73817,57 +73805,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>上市櫃產業</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>基本族群</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>主流/非主流</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>熱門族群1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>熱門族群2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>熱門族群3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>熱門族群4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>熱門族群5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_0501_1000" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1001_1500" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1501_2000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2377" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2378" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73788,7 +73788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K378"/>
+  <dimension ref="A1:K379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -79203,27 +79203,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -79231,32 +79231,36 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -79264,31 +79268,27 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -79310,22 +79310,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -79347,22 +79347,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -79384,22 +79384,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -79421,22 +79421,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -79444,44 +79444,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>半導體設備_CoWoS</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>晶圓再生</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -79489,114 +79481,122 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>半導體設備_CoWoS</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>晶圓再生</t>
+        </is>
+      </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>都有</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
+          <t>都有</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -79618,12 +79618,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -79641,40 +79641,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -79682,36 +79678,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -79719,30 +79719,26 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>被動元件</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>電容</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -79765,35 +79761,35 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>電容</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -79801,36 +79797,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>被動元件</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -79852,22 +79852,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -79875,40 +79875,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -79916,36 +79912,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -79967,22 +79967,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -80004,22 +80004,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -80041,22 +80041,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -80078,22 +80078,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -80115,22 +80115,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -80152,27 +80152,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -80180,32 +80180,36 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -80213,21 +80217,17 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -80259,22 +80259,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -80296,22 +80296,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -80333,22 +80333,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -80370,22 +80370,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -80407,22 +80407,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -80444,22 +80444,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -80481,27 +80481,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -80518,22 +80518,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>泰霖</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -80555,27 +80555,27 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>泰霖</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -80592,22 +80592,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>瑞穎</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -80629,22 +80629,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>瑞穎</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -80666,22 +80666,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -80703,22 +80703,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -80726,78 +80726,82 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>低軌衛星</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>低軌衛星</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -80805,31 +80809,27 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -80851,22 +80851,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -80888,22 +80888,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -80925,22 +80925,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -80962,22 +80962,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -80999,22 +80999,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -81036,22 +81036,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>大世科</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -81073,22 +81073,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>大世科</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -81110,22 +81110,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -81147,22 +81147,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -81184,22 +81184,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -81221,12 +81221,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -81258,22 +81258,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>大億金茂</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -81295,22 +81295,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>大億金茂</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -81332,22 +81332,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -81369,22 +81369,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -81406,22 +81406,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -81443,22 +81443,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -81480,22 +81480,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -81517,22 +81517,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -81554,22 +81554,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -81591,22 +81591,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -81614,40 +81614,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -81655,36 +81651,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -81706,22 +81706,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -81743,27 +81743,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -81771,32 +81771,36 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -81804,31 +81808,27 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -81850,22 +81850,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -81887,12 +81887,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -81924,22 +81924,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -81961,22 +81961,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -81998,22 +81998,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -82035,22 +82035,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -82058,40 +82058,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -82099,36 +82095,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -82150,22 +82150,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -82187,22 +82187,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -82224,22 +82224,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -82261,22 +82261,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>朋程</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -82284,16 +82284,8 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>功率元件/二極體</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>MOSFET</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
@@ -82306,12 +82298,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -82331,38 +82323,42 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr"/>
+          <t>功率元件/二極體</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>全景軟體</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -82370,36 +82366,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>全景軟體</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -82421,27 +82421,27 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>生展</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -82458,27 +82458,27 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>生展</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -82495,22 +82495,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>三竹</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -82532,12 +82532,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -82569,22 +82569,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -82592,73 +82592,77 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -82676,22 +82680,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>恒耀國際</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -82704,31 +82708,27 @@
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>恒耀國際</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -82741,110 +82741,110 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>冠好</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -82861,22 +82861,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -82898,27 +82898,27 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -82926,27 +82926,31 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -82964,22 +82968,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>盛弘</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -82992,31 +82996,27 @@
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>盛弘</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -83029,27 +83029,31 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -83062,36 +83066,32 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -83108,27 +83108,27 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -83136,27 +83136,31 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -83169,36 +83173,32 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>實威</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -83215,27 +83215,27 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>旭源</t>
+          <t>實威</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -83243,27 +83243,31 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>旭源</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -83281,12 +83285,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -83314,22 +83318,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -83342,31 +83346,27 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>紅木-KY</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -83379,27 +83379,31 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -83412,36 +83416,32 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -83458,27 +83458,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -83495,22 +83495,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>弘帆</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -83523,27 +83523,31 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>鉅邁</t>
+          <t>弘帆</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -83561,22 +83565,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>大江</t>
+          <t>鉅邁</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -83589,31 +83593,27 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>大地-KY</t>
+          <t>大江</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -83626,27 +83626,31 @@
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>大地-KY</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -83664,12 +83668,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -83697,22 +83701,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -83730,22 +83734,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -83758,31 +83762,27 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -83795,27 +83795,31 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>華研</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -83833,12 +83837,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>華研</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -83866,27 +83870,27 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -83894,31 +83898,27 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -83940,27 +83940,27 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -83968,27 +83968,31 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -84006,22 +84010,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -84039,22 +84043,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -84072,22 +84076,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -84105,27 +84109,27 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -84133,36 +84137,32 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -84170,17 +84170,21 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -84208,27 +84212,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -84236,36 +84240,32 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -84273,27 +84273,31 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -84311,22 +84315,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -84344,27 +84348,27 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -84372,36 +84376,32 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -84409,17 +84409,21 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>三貝德</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -84447,27 +84451,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>三貝德</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -84475,36 +84479,32 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>裕國</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -84512,17 +84512,21 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>花王</t>
+          <t>裕國</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -84550,22 +84554,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -84578,31 +84582,27 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>光隆</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -84615,27 +84615,31 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -84648,31 +84652,27 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -84685,27 +84685,31 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -84723,22 +84727,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>大田</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -84756,22 +84760,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大田</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -84784,21 +84788,17 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>北基</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -84830,22 +84830,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>鉅明</t>
+          <t>北基</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -84858,27 +84858,31 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>鉅明</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -84896,22 +84900,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>青鋼</t>
+          <t>富堡</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -84924,31 +84928,27 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>青鋼</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -84970,27 +84970,27 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -85007,27 +85007,27 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -85035,27 +85035,31 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>邦泰</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -85073,12 +85077,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -85106,12 +85110,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>合騏*</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -85139,22 +85143,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>明安</t>
+          <t>合騏*</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -85172,22 +85176,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>明安</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -85200,31 +85204,27 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>關中</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -85237,27 +85237,31 @@
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>森鉅</t>
+          <t>關中</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -85275,90 +85279,86 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>森鉅</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>散熱液冷</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>散熱液冷</t>
+        </is>
+      </c>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>910322</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>康師傅-DR</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -85390,12 +85390,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>910322</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>康師傅-DR</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -85427,12 +85427,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -85464,12 +85464,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>910861</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>神州-DR</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -85501,12 +85501,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -85538,12 +85538,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>泰聚亨-DR</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -85575,12 +85575,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>911868</t>
+          <t>911622</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>同方友友-DR</t>
+          <t>泰聚亨-DR</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -85612,12 +85612,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>912000</t>
+          <t>911868</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>晨訊科-DR</t>
+          <t>同方友友-DR</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -85649,12 +85649,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>912000</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>晨訊科-DR</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -85686,22 +85686,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -85714,27 +85714,31 @@
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -85752,22 +85756,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -85785,22 +85789,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -85818,22 +85822,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -85846,31 +85850,27 @@
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -85883,27 +85883,31 @@
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -85916,31 +85920,27 @@
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -85953,27 +85953,31 @@
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -85991,27 +85995,27 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -86019,36 +86023,32 @@
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -86056,27 +86056,31 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86094,22 +86098,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86122,31 +86126,27 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -86159,27 +86159,31 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>巨大</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -86197,22 +86201,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>福興</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -86230,22 +86234,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>福興</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -86263,22 +86267,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -86291,31 +86295,27 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>泰銘</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -86328,17 +86328,21 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>中視</t>
+          <t>泰銘</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -86366,12 +86370,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>中視</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -86399,22 +86403,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -86432,22 +86436,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86460,31 +86464,27 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86497,27 +86497,31 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>成霖</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -86535,12 +86539,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>慶豐富</t>
+          <t>成霖</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -86568,22 +86572,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>全國</t>
+          <t>慶豐富</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86596,31 +86600,27 @@
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>百和</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -86633,17 +86633,21 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>百和</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -86671,12 +86675,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -86704,22 +86708,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -86737,22 +86741,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -86770,22 +86774,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>好樂迪</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -86798,31 +86802,27 @@
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>新麗</t>
+          <t>好樂迪</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -86835,27 +86835,31 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>新麗</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -86873,22 +86877,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>三發地產</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -86901,31 +86905,27 @@
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>三發地產</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -86938,27 +86938,31 @@
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>萬國通</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -86971,36 +86975,32 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>萬國通</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -87017,27 +87017,27 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -87045,27 +87045,31 @@
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>世紀鋼</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -87078,31 +87082,27 @@
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>邁達康</t>
+          <t>世紀鋼</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -87115,27 +87115,31 @@
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>有益</t>
+          <t>邁達康</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -87148,7 +87152,40 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr">
+      <c r="K378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>有益</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
         <is>
           <t>provisional_industry_mapping</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -86685,12 +86685,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -16537,12 +16537,12 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -23934,12 +23934,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -48497,12 +48497,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -79735,12 +79735,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -86866,12 +86866,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -52806,12 +52806,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -55807,12 +55807,12 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -52156,12 +52156,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -52584,12 +52584,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -55807,12 +55807,12 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -85338,12 +85338,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -49003,12 +49003,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -52621,12 +52621,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -85338,12 +85338,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -85622,12 +85622,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85640,7 +85640,11 @@
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -44624,7 +44624,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>強生製藥</t>
+          <t>強生*</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -52732,12 +52732,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -52806,12 +52806,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -85622,12 +85622,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85640,11 +85640,7 @@
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -52621,12 +52621,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52732,12 +52732,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -85622,12 +85622,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85640,7 +85640,11 @@
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -86458,12 +86462,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -39196,27 +39196,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>永日</t>
+          <t>中光電投控</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -39233,12 +39233,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>永日</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -39270,12 +39270,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>東洋</t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -39307,12 +39307,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>雃博</t>
+          <t>東洋</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -39344,12 +39344,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>邦特</t>
+          <t>雃博</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -39381,12 +39381,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>懷特</t>
+          <t>邦特</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -39418,12 +39418,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>加捷生醫</t>
+          <t>懷特</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -39455,12 +39455,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>濟生</t>
+          <t>加捷生醫</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -39492,22 +39492,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>聯上</t>
+          <t>濟生</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -39529,22 +39529,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>聯上</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -39566,12 +39566,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>明基醫</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -39603,12 +39603,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>明基醫</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -39640,12 +39640,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>友華</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -39677,12 +39677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>優盛</t>
+          <t>友華</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -39714,12 +39714,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>優盛</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -39751,12 +39751,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>太醫</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -39788,12 +39788,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>天良</t>
+          <t>太醫</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -39825,12 +39825,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>中天</t>
+          <t>天良</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -39862,12 +39862,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>中天</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -39899,12 +39899,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>浩泰</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -39936,12 +39936,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>亞諾法</t>
+          <t>浩泰</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -39973,12 +39973,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>麗豐-KY</t>
+          <t>亞諾法</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -40010,12 +40010,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>曜亞</t>
+          <t>麗豐-KY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -40047,12 +40047,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>馬光-KY</t>
+          <t>曜亞</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -40084,12 +40084,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>國光生</t>
+          <t>馬光-KY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -40121,12 +40121,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>中裕</t>
+          <t>國光生</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -40158,12 +40158,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>全宇生技-KY</t>
+          <t>中裕</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -40195,12 +40195,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>鈺緯</t>
+          <t>全宇生技-KY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -40232,22 +40232,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>樂威科-KY</t>
+          <t>鈺緯</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -40260,27 +40260,31 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>訊映</t>
+          <t>樂威科-KY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -40293,21 +40297,17 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>太景*-KY</t>
+          <t>訊映</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -40339,12 +40339,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>訊聯基因</t>
+          <t>太景*-KY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -40376,12 +40376,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>聿新科</t>
+          <t>訊聯基因</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -40413,12 +40413,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>智擎</t>
+          <t>聿新科</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -40450,12 +40450,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>鐿鈦</t>
+          <t>智擎</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -40487,12 +40487,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>承業醫</t>
+          <t>鐿鈦</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -40524,12 +40524,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>友霖</t>
+          <t>承業醫</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -40561,12 +40561,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>松瑞藥</t>
+          <t>友霖</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -40598,12 +40598,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>醣聯</t>
+          <t>松瑞藥</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -40635,12 +40635,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>泰宗</t>
+          <t>醣聯</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -40672,22 +40672,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>瑞基</t>
+          <t>泰宗</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>農業科技</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>農業科技</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -40700,27 +40700,31 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>久裕</t>
+          <t>瑞基</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>農業科技</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>農業科技</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -40733,21 +40737,17 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>浩鼎</t>
+          <t>久裕</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -40779,12 +40779,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>杏一</t>
+          <t>浩鼎</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -40816,12 +40816,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>永笙-KY</t>
+          <t>杏一</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -40853,12 +40853,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>福永生技</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -40890,12 +40890,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>安克</t>
+          <t>福永生技</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -40927,12 +40927,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>佐登-KY</t>
+          <t>安克</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -40964,12 +40964,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>杏國</t>
+          <t>佐登-KY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -41001,12 +41001,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>基米-創</t>
+          <t>杏國</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -41038,12 +41038,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>欣大健康</t>
+          <t>基米-創</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -41075,22 +41075,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>中華食</t>
+          <t>欣大健康</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>食品工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>食品工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -41112,12 +41112,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>環泰</t>
+          <t>中華食</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -41149,22 +41149,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>環泰</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>食品工業</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>食品工業</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -41186,12 +41186,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>勝昱</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -41223,12 +41223,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>世坤</t>
+          <t>勝昱</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -41260,12 +41260,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>炎洲</t>
+          <t>世坤</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -41297,22 +41297,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>東隆興</t>
+          <t>炎洲</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -41334,12 +41334,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>郡都開發</t>
+          <t>東隆興</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -41371,12 +41371,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>新昕纖</t>
+          <t>郡都開發</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -41408,12 +41408,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>飛寶企業</t>
+          <t>新昕纖</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -41445,12 +41445,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>如興</t>
+          <t>飛寶企業</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -41482,22 +41482,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>三圓</t>
+          <t>如興</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -41519,22 +41519,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>金洲</t>
+          <t>三圓</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -41556,22 +41556,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>皇家美食</t>
+          <t>金洲</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -41593,22 +41593,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>光明</t>
+          <t>皇家美食</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -41630,12 +41630,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>利勤</t>
+          <t>光明</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -41667,22 +41667,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>耀億</t>
+          <t>利勤</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -41695,27 +41695,31 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>銘旺實</t>
+          <t>耀億</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>紡織纖維</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -41728,21 +41732,17 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>興采</t>
+          <t>銘旺實</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -41774,12 +41774,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>廣越</t>
+          <t>興采</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -41811,12 +41811,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>冠星-KY</t>
+          <t>廣越</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -41848,12 +41848,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>冠星-KY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -41885,12 +41885,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -41922,12 +41922,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>竣邦-KY</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -41959,27 +41959,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>健信</t>
+          <t>竣邦-KY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>紡織纖維</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -41996,12 +41996,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>金雨</t>
+          <t>健信</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -42033,12 +42033,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>金雨</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -42070,12 +42070,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>高鋒</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -42107,12 +42107,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>福裕</t>
+          <t>高鋒</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -42144,12 +42144,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>永彰</t>
+          <t>福裕</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -42181,12 +42181,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>東台</t>
+          <t>永彰</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -42218,12 +42218,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>方方土霖</t>
+          <t>東台</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -42255,12 +42255,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>江興鍛</t>
+          <t>方方土霖</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -42292,27 +42292,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>淳紳</t>
+          <t>江興鍛</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -42320,27 +42320,31 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>天意能創</t>
+          <t>淳紳</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -42353,36 +42357,32 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>瑞智</t>
+          <t>天意能創</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -42399,12 +42399,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>協易機</t>
+          <t>瑞智</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -42436,12 +42436,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>慶騰</t>
+          <t>協易機</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -42473,12 +42473,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>至興</t>
+          <t>慶騰</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -42510,27 +42510,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>拓凱</t>
+          <t>至興</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -42538,32 +42538,36 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>大詠城</t>
+          <t>拓凱</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -42571,21 +42575,17 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>全球傳動</t>
+          <t>大詠城</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -42617,27 +42617,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>晟田</t>
+          <t>全球傳動</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -42645,32 +42645,36 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>科嶠</t>
+          <t>晟田</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -42678,31 +42682,27 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>萬在</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -42724,22 +42724,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>萬在</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -42761,22 +42761,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>桓達</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -42798,12 +42798,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>長佳</t>
+          <t>桓達</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -42835,27 +42835,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>智伸科</t>
+          <t>長佳</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -42872,27 +42872,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>力達-KY</t>
+          <t>智伸科</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -42909,22 +42909,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>力達-KY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -42946,22 +42946,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>氣立</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -42983,27 +42983,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>旭然</t>
+          <t>氣立</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -43011,27 +43011,31 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>永新-KY</t>
+          <t>旭然</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -43044,36 +43048,32 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>寶緯</t>
+          <t>永新-KY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -43090,12 +43090,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>強信-KY</t>
+          <t>寶緯</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -43127,12 +43127,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>健椿</t>
+          <t>強信-KY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -43164,12 +43164,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>穎漢</t>
+          <t>健椿</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -43201,12 +43201,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>百德</t>
+          <t>穎漢</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -43238,12 +43238,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>元翎</t>
+          <t>百德</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -43275,12 +43275,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>時碩工業</t>
+          <t>元翎</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -43312,12 +43312,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>科際精密</t>
+          <t>時碩工業</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -43349,27 +43349,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>科際精密</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -43386,27 +43386,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>鈞興-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -43423,12 +43423,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>駐龍</t>
+          <t>鈞興-KY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -43446,30 +43446,26 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>大銀微系統</t>
+          <t>駐龍</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -43489,42 +43485,38 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>機器人</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>精密傳動</t>
-        </is>
-      </c>
+          <t>軍工無人機</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>user_confirmed_robotics_theme</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>大銀微系統</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -43532,36 +43524,44 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>機器人</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>精密傳動</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_confirmed_robotics_theme</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>捷流閥業</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -43583,27 +43583,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>光隆精密-KY</t>
+          <t>捷流閥業</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -43620,22 +43620,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>光隆精密-KY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -43648,58 +43648,54 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>機器人自動化</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>君帆</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -43717,36 +43713,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>機器人自動化</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>君帆</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -43768,12 +43768,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -43805,22 +43805,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>富田-創</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -43842,27 +43842,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>唐鋒</t>
+          <t>富田-創</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -43870,17 +43870,21 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>中美實</t>
+          <t>唐鋒</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -43908,22 +43912,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>大恭</t>
+          <t>中美實</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -43936,21 +43940,17 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>磐亞</t>
+          <t>大恭</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -43982,12 +43982,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>永純</t>
+          <t>磐亞</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -44019,12 +44019,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>永純</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -44056,12 +44056,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>大立</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -44093,12 +44093,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>德淵</t>
+          <t>大立</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -44130,12 +44130,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>德淵</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -44167,12 +44167,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>國精化</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -44204,22 +44204,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>永昕</t>
+          <t>國精化</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -44241,12 +44241,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>雙美</t>
+          <t>永昕</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -44278,27 +44278,27 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>雙美</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -44315,27 +44315,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>豪展</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -44352,12 +44352,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>泰博</t>
+          <t>豪展</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -44389,12 +44389,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>華廣</t>
+          <t>泰博</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -44426,22 +44426,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>康普</t>
+          <t>華廣</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -44463,12 +44463,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>泓瀚</t>
+          <t>康普</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -44500,22 +44500,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>合一</t>
+          <t>泓瀚</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -44537,12 +44537,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>皇將</t>
+          <t>合一</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -44574,12 +44574,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>合富-KY</t>
+          <t>皇將</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -44611,12 +44611,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>合富-KY</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -44648,12 +44648,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>強生*</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -44685,27 +44685,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>強生*</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -44722,27 +44722,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>國碳科</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -44759,12 +44759,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>國碳科</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -44796,27 +44796,27 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>勤凱科技</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -44833,27 +44833,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>勤凱科技</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -44870,12 +44870,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>雙鍵</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -44907,12 +44907,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>雙鍵</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -44944,12 +44944,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>誠泰科技</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -44981,12 +44981,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>晶呈科技</t>
+          <t>誠泰科技</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -45018,12 +45018,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>上品</t>
+          <t>晶呈科技</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -45055,22 +45055,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>望隼</t>
+          <t>上品</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -45092,22 +45092,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>台特化</t>
+          <t>望隼</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -45129,22 +45129,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>大略-KY</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -45166,22 +45166,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>桂田文創</t>
+          <t>大略-KY</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -45194,27 +45194,31 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>日成-KY</t>
+          <t>桂田文創</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -45227,36 +45231,32 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>日成-KY</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -45273,12 +45273,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -45310,27 +45310,27 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -45347,135 +45347,131 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>網通交換器</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>網通設備</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>富宇</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>網通交換器</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>網通設備</t>
+        </is>
+      </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>富宇</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>CPO光通訊</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -45493,41 +45489,45 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CPO光通訊</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>德英</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -45544,27 +45544,27 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>德英</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -45581,12 +45581,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -45618,22 +45618,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -45641,44 +45641,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>低軌衛星</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>工業電腦</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -45686,26 +45678,34 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>低軌衛星</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>工業電腦</t>
+        </is>
+      </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>力士</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -45737,27 +45737,27 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>力士</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -45765,32 +45765,36 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -45798,31 +45802,27 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -45844,22 +45844,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -45867,40 +45867,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>電源_BBU</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -45908,26 +45904,30 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>電源_BBU</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -45959,12 +45959,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -45996,22 +45996,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -46019,40 +46019,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>AI伺服器</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>亞電</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -46060,36 +46056,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>AI伺服器</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -46111,22 +46111,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -46148,27 +46148,27 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>辣椒</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -46176,32 +46176,36 @@
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>辣椒</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -46209,36 +46213,32 @@
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>金耘國際</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -46255,27 +46255,27 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>金耘國際</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -46292,12 +46292,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -46329,22 +46329,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>緯致</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -46366,22 +46366,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>緯致</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -46403,22 +46403,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -46426,44 +46426,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>車用電子</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -46471,36 +46463,44 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>車用電子</t>
+        </is>
+      </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -46522,12 +46522,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -46545,16 +46545,8 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>IC設計</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
@@ -46567,12 +46559,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -46590,8 +46582,16 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>IC設計</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
@@ -46604,12 +46604,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -46641,12 +46641,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -46678,22 +46678,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -46715,22 +46715,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>廣穎電通</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -46752,22 +46752,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>廣穎電通</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -46789,22 +46789,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -46826,22 +46826,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -46863,12 +46863,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -46886,40 +46886,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>CPO光通訊</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -46927,36 +46923,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>CPO光通訊</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -46978,22 +46978,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -47015,22 +47015,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -47052,22 +47052,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -47089,27 +47089,27 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>三星</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -47126,12 +47126,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>榮剛</t>
+          <t>三星</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -47163,12 +47163,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>久陽</t>
+          <t>榮剛</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -47200,12 +47200,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>強新</t>
+          <t>久陽</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -47237,12 +47237,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>建錩</t>
+          <t>強新</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -47274,12 +47274,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>華祺</t>
+          <t>建錩</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -47311,12 +47311,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>松和</t>
+          <t>華祺</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -47348,27 +47348,27 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>凱衛</t>
+          <t>松和</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -47385,12 +47385,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>力新</t>
+          <t>凱衛</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -47422,12 +47422,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>力新</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -47459,27 +47459,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -47487,27 +47487,31 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>坤悅</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -47520,31 +47524,27 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>新鼎</t>
+          <t>坤悅</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -47557,32 +47557,36 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>寶碩</t>
+          <t>新鼎</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -47590,21 +47594,17 @@
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>蒙恬</t>
+          <t>寶碩</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -47636,12 +47636,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>凌網</t>
+          <t>蒙恬</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -47673,27 +47673,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>亞昕</t>
+          <t>凌網</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -47710,27 +47710,27 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>亞昕</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -47747,22 +47747,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -47784,22 +47784,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -47821,22 +47821,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -47858,22 +47858,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -47895,22 +47895,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -47932,12 +47932,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -47969,22 +47969,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -48006,12 +48006,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -48043,22 +48043,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -48080,22 +48080,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -48117,12 +48117,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -48154,12 +48154,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -48191,12 +48191,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -48228,22 +48228,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -48265,27 +48265,27 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>智崴</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -48293,32 +48293,36 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>智崴</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -48326,21 +48330,17 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -48372,12 +48372,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -48409,27 +48409,27 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>達輝-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -48437,32 +48437,36 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>尚凡*</t>
+          <t>達輝-KY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -48470,31 +48474,27 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>禾聯碩</t>
+          <t>尚凡*</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>電器電纜</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -48516,27 +48516,27 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>jpp-KY</t>
+          <t>禾聯碩</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -48544,32 +48544,36 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>界霖</t>
+          <t>jpp-KY</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -48577,31 +48581,27 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>界霖</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -48623,22 +48623,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>豐祥-KY</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -48660,22 +48660,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>豐祥-KY</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -48697,22 +48697,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -48734,27 +48734,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -48762,32 +48762,36 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -48795,36 +48799,32 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>寶得利</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -48841,27 +48841,27 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>寶得利</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -48878,27 +48878,27 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>桂盟</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -48906,32 +48906,36 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>桂盟</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -48939,31 +48943,27 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>天剛</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -48985,27 +48985,27 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>寶島科</t>
+          <t>天剛</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -49022,22 +49022,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>寶島科</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -49050,32 +49050,36 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -49083,31 +49087,27 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>美而快</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -49129,27 +49129,27 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>士開</t>
+          <t>美而快</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -49166,27 +49166,27 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>士開</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -49203,12 +49203,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -49226,44 +49226,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>玻纖布</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -49271,41 +49263,49 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>玻纖布</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>馥鴻</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -49313,32 +49313,36 @@
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>馥鴻</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -49346,36 +49350,32 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -49383,72 +49383,64 @@
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>記憶體</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>DRAM IC</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -49456,8 +49448,16 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>記憶體</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>DRAM IC</t>
+        </is>
+      </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
@@ -49470,22 +49470,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -49507,22 +49507,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -49544,27 +49544,27 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>力麗店</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -49581,27 +49581,27 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>力麗店</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -52185,12 +52185,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -52613,12 +52613,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52650,12 +52650,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52835,12 +52835,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -55836,12 +55836,12 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -85651,12 +85651,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85669,11 +85669,7 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -52185,12 +52185,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -52835,12 +52835,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -42664,12 +42664,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -48563,12 +48563,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -49069,12 +49069,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -52613,12 +52613,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52650,12 +52650,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52761,12 +52761,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -68164,7 +68164,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>沛爾生醫*-創</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -85651,12 +85651,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85669,7 +85669,11 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12763,7 +12763,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>三晃</t>
+          <t>國慶科技</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -48563,12 +48563,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -49069,12 +49069,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -52185,12 +52185,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -52613,12 +52613,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52650,12 +52650,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52761,12 +52761,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -52835,12 +52835,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -42664,12 +42664,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -49069,12 +49069,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -52185,12 +52185,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -52613,12 +52613,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52650,12 +52650,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52761,12 +52761,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -52835,12 +52835,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -85651,12 +85651,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85669,11 +85669,7 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_0501_1000" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1001_1500" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1501_2000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2384" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2385" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43030,12 +43030,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -52185,12 +52185,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -73792,7 +73792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K385"/>
+  <dimension ref="A1:K386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -79273,22 +79273,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -79301,36 +79301,32 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -79347,22 +79343,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>永悅健康-創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -79384,12 +79380,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>永悅健康-創</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -79421,27 +79417,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -79449,27 +79445,31 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -79487,27 +79487,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -79515,31 +79515,27 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -79561,22 +79557,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -79598,22 +79594,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -79635,22 +79631,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -79672,22 +79668,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -79695,44 +79691,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>半導體設備_CoWoS</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>晶圓再生</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -79740,114 +79728,122 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>半導體設備_CoWoS</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>晶圓再生</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>都有</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>都有</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -79869,12 +79865,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -79892,40 +79888,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -79933,36 +79925,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -79970,30 +79966,26 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>被動元件</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>電容</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -80016,35 +80008,35 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>電容</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -80052,36 +80044,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>被動元件</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -80103,22 +80099,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -80126,40 +80122,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -80167,36 +80159,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -80218,22 +80214,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -80255,22 +80251,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -80292,22 +80288,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -80329,22 +80325,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -80366,22 +80362,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -80403,27 +80399,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -80431,32 +80427,36 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -80464,21 +80464,17 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -80510,22 +80506,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -80547,22 +80543,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -80584,22 +80580,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -80621,22 +80617,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -80658,22 +80654,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -80695,22 +80691,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -80732,27 +80728,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -80769,22 +80765,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>泰霖</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -80806,27 +80802,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>泰霖</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -80843,22 +80839,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>瑞穎</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -80880,22 +80876,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>瑞穎</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -80917,22 +80913,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -80954,22 +80950,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -80977,78 +80973,82 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>低軌衛星</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>低軌衛星</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -81056,31 +81056,27 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -81102,22 +81098,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -81139,22 +81135,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -81176,22 +81172,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -81213,22 +81209,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -81250,22 +81246,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -81287,22 +81283,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>大世科</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -81324,22 +81320,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>大世科</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -81361,22 +81357,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -81398,22 +81394,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -81435,22 +81431,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -81472,12 +81468,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -81509,22 +81505,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>大億金茂</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -81546,22 +81542,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>大億金茂</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -81583,22 +81579,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -81620,22 +81616,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -81657,22 +81653,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -81694,22 +81690,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -81731,22 +81727,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -81768,22 +81764,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -81805,22 +81801,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -81842,22 +81838,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -81865,40 +81861,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -81906,36 +81898,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -81957,22 +81953,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -81994,27 +81990,27 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -82022,32 +82018,36 @@
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -82055,31 +82055,27 @@
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -82101,22 +82097,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -82138,12 +82134,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -82175,22 +82171,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -82212,22 +82208,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -82249,22 +82245,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -82286,22 +82282,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -82309,40 +82305,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -82350,36 +82342,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -82401,22 +82397,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -82438,22 +82434,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -82475,22 +82471,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -82512,22 +82508,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>朋程</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -82535,16 +82531,8 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>功率元件/二極體</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>MOSFET</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
@@ -82557,12 +82545,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -82582,38 +82570,42 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr"/>
+          <t>功率元件/二極體</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>全景軟體</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -82621,36 +82613,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>全景軟體</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -82672,27 +82668,27 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>生展</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -82709,27 +82705,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>生展</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -82746,22 +82742,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>三竹</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -82783,12 +82779,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -82820,22 +82816,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -82843,73 +82839,77 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -82927,22 +82927,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>恒耀國際</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -82955,31 +82955,27 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>恒耀國際</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -82992,110 +82988,110 @@
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>冠好</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -83112,22 +83108,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -83149,27 +83145,27 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -83177,27 +83173,31 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -83215,22 +83215,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>盛弘</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -83243,31 +83243,27 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>盛弘</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -83280,27 +83276,31 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -83313,36 +83313,32 @@
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -83359,27 +83355,27 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -83387,27 +83383,31 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -83420,36 +83420,32 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>實威</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -83466,27 +83462,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>旭源</t>
+          <t>實威</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -83494,27 +83490,31 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>旭源</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -83532,12 +83532,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -83565,22 +83565,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -83593,31 +83593,27 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>紅木-KY</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -83630,27 +83626,31 @@
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -83663,36 +83663,32 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -83709,27 +83705,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -83746,22 +83742,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>弘帆</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -83774,27 +83770,31 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>鉅邁</t>
+          <t>弘帆</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -83812,22 +83812,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>大江</t>
+          <t>鉅邁</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -83840,31 +83840,27 @@
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>大地-KY</t>
+          <t>大江</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -83877,27 +83873,31 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>大地-KY</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -83915,12 +83915,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -83948,22 +83948,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -83981,22 +83981,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -84009,31 +84009,27 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -84046,27 +84042,31 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>華研</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -84084,12 +84084,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>華研</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -84117,27 +84117,27 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -84145,31 +84145,27 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -84191,27 +84187,27 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -84219,27 +84215,31 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -84257,22 +84257,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -84290,22 +84290,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -84323,22 +84323,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -84356,27 +84356,27 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>納維康</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -84384,36 +84384,32 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>納維康</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -84421,17 +84417,21 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -84459,27 +84459,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -84487,36 +84487,32 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -84524,27 +84520,31 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -84562,22 +84562,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -84595,27 +84595,27 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -84623,36 +84623,32 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -84660,17 +84656,21 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>三貝德</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -84698,27 +84698,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>三貝德</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -84726,36 +84726,32 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>裕國</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -84763,17 +84759,21 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>花王</t>
+          <t>裕國</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -84801,22 +84801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -84829,31 +84829,27 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>光隆</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -84866,27 +84862,31 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -84899,31 +84899,27 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -84936,27 +84932,31 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -84974,22 +84974,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>大田</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -85007,22 +85007,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大田</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -85035,21 +85035,17 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>北基</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -85081,22 +85077,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>鉅明</t>
+          <t>北基</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -85109,27 +85105,31 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>鉅明</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -85147,22 +85147,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>青鋼</t>
+          <t>富堡</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -85175,31 +85175,27 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>青鋼</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -85221,27 +85217,27 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -85258,27 +85254,27 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -85286,27 +85282,31 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>邦泰</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -85324,12 +85324,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -85357,12 +85357,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>合騏*</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -85390,22 +85390,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>明安</t>
+          <t>合騏*</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -85423,22 +85423,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>明安</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -85451,31 +85451,27 @@
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>關中</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -85488,27 +85484,31 @@
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>森鉅</t>
+          <t>關中</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -85526,90 +85526,86 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>森鉅</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>散熱液冷</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>散熱液冷</t>
+        </is>
+      </c>
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>910322</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>康師傅-DR</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -85641,22 +85637,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>910322</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>康師傅-DR</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85669,17 +85665,21 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -85711,12 +85711,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>910861</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>神州-DR</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -85748,12 +85748,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -85785,12 +85785,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>泰聚亨-DR</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -85822,12 +85822,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>911868</t>
+          <t>911622</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>同方友友-DR</t>
+          <t>泰聚亨-DR</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -85859,12 +85859,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>912000</t>
+          <t>911868</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>晨訊科-DR</t>
+          <t>同方友友-DR</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -85896,12 +85896,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>912000</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>晨訊科-DR</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -85933,22 +85933,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -85961,27 +85961,31 @@
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -85999,22 +86003,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -86032,22 +86036,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86065,22 +86069,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86093,31 +86097,27 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86130,27 +86130,31 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -86163,31 +86167,27 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -86200,27 +86200,31 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -86238,27 +86242,27 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -86266,36 +86270,32 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -86303,27 +86303,31 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -86341,22 +86345,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -86369,31 +86373,27 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -86406,27 +86406,31 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>巨大</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -86444,22 +86448,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>福興</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86477,22 +86481,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>福興</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86510,22 +86514,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -86538,31 +86542,27 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>泰銘</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -86575,17 +86575,21 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>中視</t>
+          <t>泰銘</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -86613,12 +86617,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>中視</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -86646,22 +86650,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86679,22 +86683,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -86707,31 +86711,27 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -86744,27 +86744,31 @@
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>成霖</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -86782,12 +86786,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>慶豐富</t>
+          <t>成霖</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -86815,22 +86819,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>全國</t>
+          <t>慶豐富</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -86843,31 +86847,27 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>百和</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -86880,17 +86880,21 @@
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>百和</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -86918,12 +86922,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -86951,22 +86955,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -86984,22 +86988,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -87017,22 +87021,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>好樂迪</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -87045,31 +87049,27 @@
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>新麗</t>
+          <t>好樂迪</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -87082,27 +87082,31 @@
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>新麗</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -87120,22 +87124,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>三發地產</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -87148,31 +87152,27 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>三發地產</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -87185,27 +87185,31 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>萬國通</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -87218,36 +87222,32 @@
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>萬國通</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F381" t="inlineStr"/>
@@ -87264,27 +87264,27 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -87292,27 +87292,31 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>世紀鋼</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -87325,31 +87329,27 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>邁達康</t>
+          <t>世紀鋼</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -87362,27 +87362,31 @@
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>有益</t>
+          <t>邁達康</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -87395,7 +87399,40 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr">
+      <c r="K385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>有益</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
         <is>
           <t>provisional_industry_mapping</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -42664,12 +42664,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -52613,12 +52613,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -52650,12 +52650,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52761,12 +52761,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -79283,17 +79283,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -79301,7 +79301,11 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -79797,12 +79801,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -85684,12 +85688,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -85702,11 +85706,7 @@
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
